--- a/fieldSelectionPriorityList.xlsx
+++ b/fieldSelectionPriorityList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Career\00. Univesity\PHD\5. Field selection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Career\00. Univesity\PHD\2. Exam Log\blackoutPhdPreparation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F48ACA-2D7B-4520-9B76-3593B85D7BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1D4F5F-27FD-42EA-A721-C265D4AEE8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C41F7097-CAB5-4071-B473-853C504AEB75}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="70">
   <si>
     <t>Priority</t>
   </si>
@@ -522,37 +522,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -572,6 +551,27 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1251,223 +1251,223 @@
   <sheetData>
     <row r="1" spans="3:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="3:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6" t="s">
+      <c r="D2" s="15"/>
+      <c r="E2" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="7"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="4" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C4" s="10">
+      <c r="C4" s="20">
         <v>1</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="18">
         <f>C11+1</f>
         <v>9</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>61</v>
+      <c r="F4" s="12" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C5" s="10">
+      <c r="C5" s="20">
         <v>2</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="18">
         <f>E4+1</f>
         <v>10</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>5</v>
+      <c r="F5" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C6" s="10">
+      <c r="C6" s="20">
         <v>3</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="18">
         <f t="shared" ref="E6:E18" si="0">E5+1</f>
         <v>11</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C7" s="20">
+        <v>4</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="18">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C8" s="20">
+        <v>5</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="18">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C9" s="20">
+        <v>6</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="18">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C10" s="20">
+        <v>7</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="18">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C11" s="20">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C7" s="10">
-        <v>4</v>
-      </c>
-      <c r="D7" s="16" t="s">
+      <c r="D11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="18">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C12" s="6"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C13" s="6"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="18">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C14" s="6"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="18">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="6"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="18">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="E7" s="11">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C8" s="10">
-        <v>5</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="11">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C9" s="10">
-        <v>6</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="11">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C10" s="10">
-        <v>7</v>
-      </c>
-      <c r="D10" s="16" t="s">
+      <c r="F15" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C16" s="6"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="18">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="E10" s="11">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C11" s="10">
-        <v>8</v>
-      </c>
-      <c r="D11" s="16" t="s">
+      <c r="F16" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C17" s="6"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="18">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="E11" s="11">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C12" s="12"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="11">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C13" s="12"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="11">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C14" s="12"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="11">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C15" s="12"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="11">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C16" s="12"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="11">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C17" s="12"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="11">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="12" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="3:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C18" s="13"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="14">
+      <c r="C18" s="7"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="19">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="13" t="s">
         <v>13</v>
       </c>
     </row>

--- a/fieldSelectionPriorityList.xlsx
+++ b/fieldSelectionPriorityList.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Career\00. Univesity\PHD\2. Exam Log\blackoutPhdPreparation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1D4F5F-27FD-42EA-A721-C265D4AEE8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E0BC57-A3BC-4941-A570-B94843F94771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C41F7097-CAB5-4071-B473-853C504AEB75}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C41F7097-CAB5-4071-B473-853C504AEB75}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -254,7 +254,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,8 +285,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -317,8 +325,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -462,52 +482,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -517,17 +494,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -546,24 +517,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -572,6 +525,36 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -927,6 +910,256 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89B8EF23-82C7-4DEE-B412-82D6FA1F0835}">
+  <dimension ref="C2:F19"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="54" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="60.6640625" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C2" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="15"/>
+      <c r="E2" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="17"/>
+    </row>
+    <row r="3" spans="3:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+    </row>
+    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C4" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C5" s="12">
+        <v>1</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="10">
+        <f>C12+1</f>
+        <v>9</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C6" s="12">
+        <v>2</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="10">
+        <f>E5+1</f>
+        <v>10</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C7" s="12">
+        <v>3</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" ref="E7:E19" si="0">E6+1</f>
+        <v>11</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C8" s="12">
+        <v>4</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C9" s="12">
+        <v>5</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="10">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C10" s="12">
+        <v>6</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="10">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C11" s="12">
+        <v>7</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="10">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C12" s="12">
+        <v>8</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="10">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C13" s="4"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="10">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C14" s="4"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="10">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="4"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="10">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C16" s="4"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C17" s="4"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="10">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C18" s="4"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="10">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C19" s="5"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="11">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="E2:F3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0432113F-1E3B-4570-A64A-8707EB4DED42}">
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1232,251 +1465,6 @@
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89B8EF23-82C7-4DEE-B412-82D6FA1F0835}">
-  <dimension ref="C1:F18"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="54" style="3" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="60.6640625" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="3:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="3:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C2" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="17"/>
-    </row>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="18">
-        <f>C11+1</f>
-        <v>9</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C5" s="20">
-        <v>2</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="18">
-        <f>E4+1</f>
-        <v>10</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C6" s="20">
-        <v>3</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="18">
-        <f t="shared" ref="E6:E18" si="0">E5+1</f>
-        <v>11</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C7" s="20">
-        <v>4</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="18">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C8" s="20">
-        <v>5</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="18">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C9" s="20">
-        <v>6</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="18">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C10" s="20">
-        <v>7</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="18">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C11" s="20">
-        <v>8</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="18">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C12" s="6"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="18">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C13" s="6"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="18">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C14" s="6"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="18">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C15" s="6"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="18">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C16" s="6"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="18">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C17" s="6"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="18">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="3:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C18" s="7"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="19">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
